--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$215</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1732,32 +1732,32 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1769,27 +1769,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
+          <t>5º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1806,32 +1806,32 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1843,27 +1843,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1885,22 +1885,22 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 13)</t>
+          <t>7º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -1917,27 +1917,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Qui / Fab (Fabio Merçon)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2028,27 +2028,27 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 17)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -2505,32 +2505,32 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2547,22 +2547,22 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 12)</t>
+          <t>4º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -2579,27 +2579,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2653,27 +2653,27 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 13)</t>
+          <t>6º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Raf (Rafael Alverne Freitas de Albuquerque) a cessão do(s) tempo(s) 1º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2690,27 +2690,27 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 13)</t>
+          <t>7º tempo(s) (Sex, semana 13)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Raf (Rafael Alverne Freitas de Albuquerque) a cessão do(s) tempo(s) 7º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2727,27 +2727,27 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Qui / Fab (Fabio Merçon)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Sex, semana 13)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Raf (Rafael Alverne Freitas de Albuquerque) a cessão do(s) tempo(s) 7º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2764,27 +2764,27 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 14)</t>
+          <t>7º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -2801,27 +2801,27 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qui, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 17)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 17)</t>
+          <t>7º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -4015,22 +4015,22 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 15)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -4042,37 +4042,37 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 15)</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4084,27 +4084,27 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -4121,32 +4121,32 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4200,22 +4200,22 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>3º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -4232,34 +4232,26 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>FBri (Fábio Luís de Brito)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr"/>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -4269,26 +4261,34 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 10C1</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -4298,32 +4298,32 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>2º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4335,27 +4335,27 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -4409,27 +4409,23 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr"/>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -4446,23 +4442,27 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -4479,27 +4479,27 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -4516,27 +4516,27 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4558,22 +4558,22 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -4590,34 +4590,26 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr"/>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -4961,22 +4953,22 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 15)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -4988,35 +4980,39 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 4)</t>
+          <t>11º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G103" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -5026,34 +5022,30 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>6º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -5063,27 +5055,27 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 5)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 11º de Fis para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5105,18 +5097,22 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 11º de Fis para a prova de Hist</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -5133,27 +5129,23 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -5175,18 +5167,22 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr"/>
+          <t>9º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -5203,27 +5199,23 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -5240,28 +5232,32 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr"/>
+          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5273,32 +5269,28 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr"/>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5315,22 +5307,22 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -5347,28 +5339,32 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5380,32 +5376,28 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr"/>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5422,22 +5414,22 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -5454,27 +5446,27 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 8)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -5491,27 +5483,27 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -5528,30 +5520,34 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 9)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -5561,34 +5557,30 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>8º tempo(s) (Ter, semana 9)</t>
+          <t>6º tempo(s) (Seg, semana 9)</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 8º de Qui para a prova de LP/LIT/RED</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -5598,27 +5590,27 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 9)</t>
+          <t>6º tempo(s) (Seg, semana 10)</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 9º de Bio para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -5640,22 +5632,22 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 10)</t>
+          <t>7º tempo(s) (Seg, semana 10)</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -5672,27 +5664,27 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 10)</t>
+          <t>9º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 9º de Bio para a prova de Hist</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -5714,22 +5706,22 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 12)</t>
+          <t>10º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 9º de Bio para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Hist</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -5746,27 +5738,27 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
+          <t>4º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 4º de Geo para a prova de Soc</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5783,32 +5775,28 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 12)</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr"/>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 4º de Geo para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5820,28 +5808,32 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr"/>
+          <t>9º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5853,23 +5845,23 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr"/>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -5956,27 +5948,23 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -5998,22 +5986,22 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>4º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -6030,27 +6018,27 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -6072,22 +6060,22 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>1º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -6099,37 +6087,37 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6146,22 +6134,22 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Geo</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -6178,23 +6166,27 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Geo</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
@@ -6211,23 +6203,23 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+          <t>12º tempo(s) (Ter, semana 5)</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -6244,27 +6236,23 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -6281,28 +6269,32 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6314,32 +6306,28 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr"/>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6351,28 +6339,32 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6384,32 +6376,28 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr"/>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6421,27 +6409,27 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 8)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -6458,27 +6446,27 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qua, semana 8)</t>
+          <t>2º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
@@ -6495,12 +6483,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>8º tempo(s) (Ter, semana 9)</t>
+          <t>9º tempo(s) (Qua, semana 8)</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -6515,7 +6503,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 8º de Fis para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -6532,27 +6520,27 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 9)</t>
+          <t>6º tempo(s) (Seg, semana 10)</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -6569,34 +6557,30 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 10)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G147" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -6606,30 +6590,34 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
+          <t>9º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Hist</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -6639,27 +6627,27 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -6676,32 +6664,28 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6713,28 +6697,28 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6746,27 +6730,27 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 14)</t>
+          <t>9º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
@@ -6783,23 +6767,27 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -6816,32 +6804,28 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6853,12 +6837,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -6873,7 +6857,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -6890,12 +6874,12 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
+          <t>3º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr"/>
@@ -6906,12 +6890,12 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6981,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 4)</t>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr"/>
@@ -7013,12 +6997,12 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7137,12 +7121,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 5)</t>
+          <t>5º tempo(s) (Ter, semana 5)</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr"/>
@@ -7153,12 +7137,12 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7458,27 +7442,27 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qua, semana 9)</t>
+          <t>2º tempo(s) (Sex, semana 9)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 4º de Fis para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -7500,22 +7484,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 9)</t>
+          <t>3º tempo(s) (Sex, semana 9)</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7532,32 +7516,32 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 9)</t>
+          <t>10º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7569,27 +7553,23 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr"/>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -7606,32 +7586,32 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 10)</t>
+          <t>11º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7643,23 +7623,27 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -7676,27 +7660,27 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
+          <t>3º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
@@ -7713,27 +7697,27 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -8071,12 +8055,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 4)</t>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr"/>
@@ -8087,12 +8071,12 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8104,23 +8088,27 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
@@ -8137,27 +8125,23 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr"/>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8179,22 +8163,22 @@
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
@@ -8211,23 +8195,27 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>Isb (Isabela Gomes Bustamante)</t>
+        </is>
+      </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -8244,32 +8232,28 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr"/>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8532,27 +8516,27 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Sex, semana 9)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
@@ -8574,22 +8558,22 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 9)</t>
+          <t>3º tempo(s) (Sex, semana 9)</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -8606,32 +8590,32 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 9)</t>
+          <t>10º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8643,27 +8627,23 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr"/>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -8680,32 +8660,32 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 10)</t>
+          <t>10º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G206" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8717,23 +8697,27 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 12)</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -8750,27 +8734,27 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G208" s="6" t="inlineStr">
@@ -9049,7 +9033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9469,24 +9453,24 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -9508,51 +9492,51 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Redação / AMu (André Barros Mucci)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -9562,63 +9546,63 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Port / Deb (Debora Borba Linhares)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 5</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Redação / AMu (André Barros Mucci)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Redação / AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -9628,19 +9612,19 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -9650,39 +9634,105 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Redação / AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>9C1</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Port / Jana (Janaína Souza Silva)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>9C1</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>9C1</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>9C2</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D29"/>
+  <autoFilter ref="A2:D32"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -7442,32 +7442,32 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 9)</t>
+          <t>10º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7484,22 +7484,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 9)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7516,32 +7516,32 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8516,32 +8516,32 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 9)</t>
+          <t>10º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 9)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -8590,32 +8590,32 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -7447,7 +7447,7 @@
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 10)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 9)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -8503,10 +8503,14 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G201" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 12C1</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -8516,12 +8520,12 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 10)</t>
+          <t>4º tempo(s) (Seg, semana 10)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -8536,14 +8540,10 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
-        </is>
-      </c>
-      <c r="G202" s="6" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$215</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1265,7 +1265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G215"/>
+  <dimension ref="A1:G213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5092,27 +5092,27 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 5)</t>
+          <t>9º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 11º de Fis para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -5129,23 +5129,23 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 5)</t>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -5162,27 +5162,27 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 5)</t>
+          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -5199,28 +5199,28 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+          <t>7º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5232,27 +5232,27 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -5269,28 +5269,32 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5302,32 +5306,28 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr"/>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5339,27 +5339,27 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -5376,28 +5376,32 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5409,27 +5413,27 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
+          <t>3º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -5446,27 +5450,27 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -5483,34 +5487,30 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 8)</t>
+          <t>6º tempo(s) (Seg, semana 9)</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -5520,27 +5520,27 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -5557,30 +5557,34 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 9)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -5590,27 +5594,27 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 10)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -5627,27 +5631,27 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 10)</t>
+          <t>4º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 4º de Geo para a prova de Soc</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -5664,32 +5668,28 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 9º de Bio para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5701,27 +5701,27 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
+          <t>9º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -5738,27 +5738,23 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 12)</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr"/>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 4º de Geo para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5775,28 +5771,32 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5808,32 +5808,28 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5845,23 +5841,27 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr"/>
+          <t>6º tempo(s) (Seg, semana 16)</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -5878,27 +5878,27 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>7º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
+          <t>3º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr"/>
@@ -5931,12 +5931,12 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5948,23 +5948,27 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr"/>
+          <t>4º tempo(s) (Qui, semana 16)</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -5986,22 +5990,22 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -6018,27 +6022,27 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>1º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -6060,22 +6064,22 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -6087,37 +6091,37 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>1º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6129,27 +6133,23 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr"/>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -6166,17 +6166,17 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
@@ -6203,28 +6203,28 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 5)</t>
+          <t>7º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6236,23 +6236,27 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -6269,32 +6273,28 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6306,28 +6306,32 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6339,27 +6343,27 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -6376,28 +6380,32 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr"/>
+          <t>9º tempo(s) (Qua, semana 8)</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6409,27 +6417,27 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -6446,34 +6454,30 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 8)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -6483,27 +6487,27 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qua, semana 8)</t>
+          <t>1º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -6520,27 +6524,27 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -6557,30 +6561,30 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr"/>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G147" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 11C1</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -6590,27 +6594,23 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr"/>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
@@ -6627,27 +6627,27 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -6664,28 +6664,32 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6697,28 +6701,28 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+          <t>5º tempo(s) (Qua, semana 15)</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6730,27 +6734,27 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
@@ -6767,12 +6771,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -6787,7 +6791,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -6804,12 +6808,12 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
+          <t>3º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr"/>
@@ -6820,12 +6824,12 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6837,27 +6841,27 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 16)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -6874,23 +6878,27 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
@@ -6902,74 +6910,66 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr"/>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6981,23 +6981,27 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -7014,23 +7018,27 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
@@ -7047,32 +7055,28 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr"/>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7084,34 +7088,30 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -7121,28 +7121,32 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7154,30 +7158,30 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr"/>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G164" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -7187,27 +7191,27 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
+          <t>4º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -7224,23 +7228,27 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 6)</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
@@ -7257,27 +7265,27 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -7294,32 +7302,32 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7331,27 +7339,27 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -7368,27 +7376,27 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
@@ -7405,27 +7413,27 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 7)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -7442,32 +7450,32 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7479,27 +7487,23 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr"/>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7516,27 +7520,27 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>11º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7553,23 +7557,27 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -7586,27 +7594,27 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
+          <t>3º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
@@ -7623,7 +7631,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -7660,27 +7668,23 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 12)</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>Fab (Fabio Merçon)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr"/>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
@@ -7697,27 +7701,27 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -7734,28 +7738,32 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7767,27 +7775,27 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -7804,34 +7812,30 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G182" s="6" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -7841,27 +7845,27 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -7878,30 +7882,34 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 14)</t>
+          <t>5º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G184" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -7911,27 +7919,27 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -7943,74 +7951,66 @@
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
+          <t>4º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr"/>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8022,30 +8022,34 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 4)</t>
+          <t>11º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G188" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -8055,23 +8059,23 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr"/>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -8088,27 +8092,27 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
@@ -8125,23 +8129,27 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>Isb (Isabela Gomes Bustamante)</t>
+        </is>
+      </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8158,32 +8166,28 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D192" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr"/>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8195,27 +8199,23 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr">
-        <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr"/>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -8232,28 +8232,32 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8265,23 +8269,27 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -8298,27 +8306,27 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
@@ -8335,32 +8343,32 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8372,27 +8380,27 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
@@ -8409,27 +8417,27 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -8446,34 +8454,30 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>4º tempo(s) (Seg, semana 10)</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
-        </is>
-      </c>
-      <c r="G200" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -8483,32 +8487,32 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8520,30 +8524,34 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G202" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -8553,27 +8561,23 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -8590,27 +8594,27 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>10º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
@@ -8627,23 +8631,27 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 12)</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -8660,27 +8668,27 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qua, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G206" s="6" t="inlineStr">
@@ -8697,27 +8705,23 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr"/>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -8734,32 +8738,32 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G208" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8771,23 +8775,27 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -8804,32 +8812,32 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G210" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8841,27 +8849,27 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -8878,27 +8886,27 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G212" s="6" t="inlineStr">
@@ -8915,27 +8923,27 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -8944,82 +8952,8 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C214" s="5" t="inlineStr">
-        <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D214" s="6" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="inlineStr">
-        <is>
-          <t>Fis</t>
-        </is>
-      </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G214" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C215" s="3" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D215" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F215" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G215" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G215"/>
+  <autoFilter ref="A2:G213"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -9033,7 +8967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9475,17 +9409,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 3)</t>
         </is>
       </c>
     </row>
@@ -9497,61 +9431,61 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9497,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -9573,51 +9507,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Redação / AMu (André Barros Mucci)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9563,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -9639,36 +9573,36 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -9678,12 +9612,12 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Redação / AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
         </is>
       </c>
     </row>
@@ -9695,44 +9629,88 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>9C1</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>9C1</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
           <t>9C2</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D32"/>
+  <autoFilter ref="A2:D34"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Regras relaxadas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$211</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1049,17 +1049,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>11C1/11C2</t>
+          <t>12C1/12C2</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Soc</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Coordenada (professor comum, tempos diferentes)</t>
+          <t>Já combinada (grupo paralelo)</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>LP/LIT/RED</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Já combinada (grupo paralelo)</t>
+          <t>Coordenada (professor comum, tempos diferentes)</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>LP/LIT/RED</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fil</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Fil</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Soc</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1233,25 +1233,8 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>12C1/12C2</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Soc</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Coordenada (professor comum, tempos diferentes)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:C46"/>
+  <autoFilter ref="A2:C45"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -1265,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G213"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5631,32 +5614,28 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 12)</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 4º de Geo para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5668,28 +5647,32 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr"/>
+          <t>9º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5706,22 +5689,18 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr"/>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -5738,23 +5717,27 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5771,32 +5754,28 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr"/>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5808,28 +5787,32 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr"/>
+          <t>6º tempo(s) (Seg, semana 16)</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5846,22 +5829,22 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>7º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -5878,27 +5861,23 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -5915,23 +5894,27 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Qui, semana 16)</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -5953,22 +5936,22 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -5985,27 +5968,27 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>1º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -6027,22 +6010,22 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -6054,37 +6037,37 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>1º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6096,27 +6079,23 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 5)</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -6133,23 +6112,27 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -6166,32 +6149,28 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6203,28 +6182,32 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6236,32 +6219,28 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6273,28 +6252,32 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6306,27 +6289,27 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>2º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
@@ -6343,27 +6326,27 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 8)</t>
+          <t>9º tempo(s) (Qua, semana 8)</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -6380,27 +6363,27 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qua, semana 8)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
@@ -6417,34 +6400,30 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -6454,30 +6433,34 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
+          <t>1º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -6487,32 +6470,28 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 12)</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr"/>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6524,27 +6503,23 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -6561,28 +6536,32 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr"/>
+          <t>9º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6594,23 +6573,27 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
@@ -6627,32 +6610,28 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6664,27 +6643,27 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
@@ -6701,28 +6680,32 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6734,27 +6717,23 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr"/>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
@@ -6771,27 +6750,27 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 16)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -6808,23 +6787,27 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
@@ -6836,74 +6819,66 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr"/>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6915,23 +6890,27 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -6948,23 +6927,27 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
@@ -6981,32 +6964,28 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr"/>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7018,34 +6997,30 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -7055,28 +7030,32 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7088,30 +7067,30 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr"/>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -7121,27 +7100,27 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
+          <t>4º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -7158,23 +7137,27 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 6)</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
@@ -7191,27 +7174,27 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -7228,32 +7211,32 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7265,27 +7248,27 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -7302,27 +7285,27 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
@@ -7339,27 +7322,27 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 7)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -7376,32 +7359,32 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7413,27 +7396,23 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr"/>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -7450,27 +7429,27 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>11º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -7487,23 +7466,27 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7520,27 +7503,27 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
+          <t>3º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7557,7 +7540,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -7594,27 +7577,23 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 12)</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="inlineStr">
-        <is>
-          <t>Fab (Fabio Merçon)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr"/>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
@@ -7631,27 +7610,27 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -7668,28 +7647,32 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7701,27 +7684,27 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -7738,34 +7721,30 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G180" s="6" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -7775,27 +7754,27 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -7812,30 +7791,34 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 14)</t>
+          <t>5º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G182" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -7845,27 +7828,27 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -7877,74 +7860,66 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
+          <t>4º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
-        </is>
-      </c>
-      <c r="G184" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr"/>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7956,30 +7931,34 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 4)</t>
+          <t>11º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -7989,23 +7968,23 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr"/>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -8022,27 +8001,27 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
@@ -8059,23 +8038,27 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>Isb (Isabela Gomes Bustamante)</t>
+        </is>
+      </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -8092,32 +8075,28 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr"/>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8129,27 +8108,23 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr">
-        <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr"/>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8166,28 +8141,32 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D192" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8199,23 +8178,27 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -8232,27 +8215,27 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
@@ -8269,32 +8252,32 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8306,27 +8289,27 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
@@ -8343,27 +8326,27 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -8380,34 +8363,30 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>4º tempo(s) (Seg, semana 10)</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
-        </is>
-      </c>
-      <c r="G198" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -8417,32 +8396,32 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8454,30 +8433,34 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G200" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -8487,27 +8470,23 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr"/>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -8524,27 +8503,27 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>10º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
@@ -8561,23 +8540,27 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 12)</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -8594,27 +8577,27 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qua, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
@@ -8631,27 +8614,23 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr"/>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -8668,32 +8647,32 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G206" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8705,23 +8684,27 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -8738,32 +8721,32 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G208" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8775,27 +8758,27 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -8812,27 +8795,27 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G210" s="6" t="inlineStr">
@@ -8849,27 +8832,27 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -8878,82 +8861,8 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D212" s="6" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="E212" s="5" t="inlineStr">
-        <is>
-          <t>Fis</t>
-        </is>
-      </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D213" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F213" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G213" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G213"/>
+  <autoFilter ref="A2:G211"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G211"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7721,30 +7721,34 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G180" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -7759,22 +7763,22 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>5º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -7791,27 +7795,27 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
@@ -7823,39 +7827,35 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
+          <t>4º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G183" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -7865,30 +7865,30 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 4)</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr"/>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G184" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -7903,18 +7903,22 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -7931,27 +7935,23 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr"/>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
@@ -7968,23 +7968,27 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -8006,22 +8010,22 @@
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
@@ -8038,32 +8042,28 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr">
-        <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr"/>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8075,28 +8075,28 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
+          <t>12º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr"/>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8108,23 +8108,27 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8141,27 +8145,27 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
@@ -8183,22 +8187,22 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -8215,32 +8219,32 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8252,32 +8256,32 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8289,32 +8293,32 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8326,32 +8330,32 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8363,30 +8367,34 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G198" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -8396,27 +8404,23 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -8433,27 +8437,27 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>10º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -8470,23 +8474,27 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 12)</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -8503,27 +8511,27 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qua, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
@@ -8540,27 +8548,23 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -8577,32 +8581,32 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8614,23 +8618,27 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -8647,32 +8655,32 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G206" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8684,27 +8692,27 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -8721,27 +8729,27 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G208" s="6" t="inlineStr">
@@ -8758,27 +8766,27 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -8787,82 +8795,8 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B210" s="6" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D210" s="6" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="E210" s="5" t="inlineStr">
-        <is>
-          <t>Fis</t>
-        </is>
-      </c>
-      <c r="F210" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G210" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B211" s="4" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D211" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F211" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G211" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G211"/>
+  <autoFilter ref="A2:G209"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -7837,25 +7837,29 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 4)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G183" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G211"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7721,30 +7721,34 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G180" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -7759,22 +7763,22 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>5º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -7791,27 +7795,27 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
@@ -7823,37 +7827,37 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
@@ -7865,30 +7869,30 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 4)</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr"/>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G184" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -7903,18 +7907,22 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -7931,27 +7939,23 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr"/>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
@@ -7968,23 +7972,27 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -8006,22 +8014,22 @@
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
@@ -8038,32 +8046,28 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr">
-        <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr"/>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8075,28 +8079,28 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
+          <t>12º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr"/>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8108,23 +8112,27 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8141,27 +8149,27 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
@@ -8183,22 +8191,22 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -8215,32 +8223,32 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8252,32 +8260,32 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8289,32 +8297,32 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8326,32 +8334,32 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8363,30 +8371,34 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G198" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -8396,27 +8408,23 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -8433,27 +8441,27 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>10º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -8470,23 +8478,27 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 12)</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -8503,27 +8515,27 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qua, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
@@ -8540,27 +8552,23 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -8577,32 +8585,32 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8614,23 +8622,27 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -8647,32 +8659,32 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G206" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8684,27 +8696,27 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -8721,27 +8733,27 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G208" s="6" t="inlineStr">
@@ -8758,27 +8770,27 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -8787,82 +8799,8 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B210" s="6" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C210" s="5" t="inlineStr">
-        <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D210" s="6" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="E210" s="5" t="inlineStr">
-        <is>
-          <t>Fis</t>
-        </is>
-      </c>
-      <c r="F210" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G210" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B211" s="4" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D211" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F211" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G211" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G211"/>
+  <autoFilter ref="A2:G209"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$209</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1349,32 +1349,32 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 4)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 4º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1386,32 +1386,32 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 5)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1423,32 +1423,32 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1460,27 +1460,27 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 6)</t>
+          <t>6º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1502,22 +1502,22 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 6)</t>
+          <t>7º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1534,32 +1534,32 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
+          <t>4º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 4º de Hist para a prova de DaF</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1571,32 +1571,28 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 7)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 4º de Hist para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1613,18 +1609,22 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1641,32 +1641,32 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1678,27 +1678,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 8)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 4º de DaF para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1715,32 +1715,32 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1752,27 +1752,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 12)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
+          <t>6º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1831,22 +1831,22 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 13)</t>
+          <t>7º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1863,27 +1863,27 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Qui / Fab (Fabio Merçon)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1974,27 +1974,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2196,32 +2196,32 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 4)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 4º de DaF para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2270,32 +2270,32 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2307,27 +2307,27 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 6)</t>
+          <t>6º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -2344,32 +2344,32 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 6)</t>
+          <t>4º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de DaF</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2381,32 +2381,28 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 7)</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2418,28 +2414,32 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2451,27 +2451,27 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 8)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 4º de DaF para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -2488,32 +2488,32 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2530,22 +2530,22 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
+          <t>5º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -2562,27 +2562,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2599,27 +2599,27 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -2636,27 +2636,27 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 13)</t>
+          <t>7º tempo(s) (Sex, semana 13)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Raf (Rafael Alverne Freitas de Albuquerque) a cessão do(s) tempo(s) 7º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2673,27 +2673,27 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Qui / Fab (Fabio Merçon)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Sex, semana 13)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Raf (Rafael Alverne Freitas de Albuquerque) a cessão do(s) tempo(s) 7º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2710,27 +2710,27 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 14)</t>
+          <t>7º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2747,27 +2747,27 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qui, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -8814,7 +8814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
@@ -9537,27 +9537,71 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>9C1</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
           <t>9C2</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D34"/>
+  <autoFilter ref="A2:D36"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$209</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1534,32 +1534,28 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 7)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 4º de Hist para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1576,18 +1572,22 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1604,32 +1604,32 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1678,32 +1678,32 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1715,32 +1715,32 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 12)</t>
+          <t>4º tempo(s) (Ter, semana 13)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 4º de Hist para a prova de DaF</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1752,27 +1752,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
+          <t>6º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 13)</t>
+          <t>7º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Qui / Fab (Fabio Merçon)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Redação</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1969,86 +1969,86 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
+          <t>4º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2073,44 +2073,44 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2122,27 +2122,27 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 4)</t>
+          <t>9º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2159,27 +2159,27 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 4)</t>
+          <t>6º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -2196,27 +2196,23 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2270,27 +2266,27 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 6)</t>
+          <t>4º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -2307,27 +2303,27 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 6)</t>
+          <t>5º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -2344,32 +2340,32 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2381,28 +2377,32 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
+          <t>4º tempo(s) (Ter, semana 13)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de DaF</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2414,32 +2414,32 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2488,27 +2488,27 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -2525,27 +2525,27 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 12)</t>
+          <t>7º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -2562,27 +2562,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Redação</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2599,27 +2599,27 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 13)</t>
+          <t>7º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 7º de Hist para a prova de Redação</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -2631,244 +2631,244 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Qui / Fab (Fabio Merçon)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Sex, semana 13)</t>
+          <t>4º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Raf (Rafael Alverne Freitas de Albuquerque) a cessão do(s) tempo(s) 7º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 14)</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qui, semana 14)</t>
+          <t>6º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>3º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2878,49 +2878,49 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 7º de Hist para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -2932,27 +2932,27 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 4)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -2969,27 +2969,27 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -3006,27 +3006,23 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -3043,32 +3039,32 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>10º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3080,27 +3076,27 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Sex, semana 9)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -3117,27 +3113,27 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>4º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -3154,32 +3150,32 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 5)</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3191,32 +3187,32 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3228,34 +3224,30 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
+          <t>4º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -3265,32 +3257,32 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3299,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
+          <t>9º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -3340,7 +3332,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 7)</t>
+          <t>10º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -3372,27 +3364,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 9)</t>
+          <t>1º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3409,27 +3401,27 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 10)</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -3446,27 +3438,27 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -3483,27 +3475,27 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -3520,30 +3512,34 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 12)</t>
+          <t>10º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -3553,32 +3549,32 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3590,28 +3586,32 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Qua, semana 14)</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3623,27 +3623,27 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 12)</t>
+          <t>4º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -3660,27 +3660,27 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 13)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -3697,27 +3697,27 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3729,296 +3729,288 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
+          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 14)</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>3º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 15)</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr"/>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4030,27 +4022,27 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -4067,27 +4059,27 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -4104,32 +4096,28 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4141,27 +4129,27 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -4178,27 +4166,27 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -4215,26 +4203,34 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -4244,32 +4240,32 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4281,34 +4277,26 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr"/>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -4318,32 +4306,32 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4355,27 +4343,23 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr"/>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -4392,23 +4376,27 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Seg, semana 13)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -4425,27 +4413,27 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -4462,27 +4450,27 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>1º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -4499,27 +4487,27 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4536,27 +4524,27 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -4573,26 +4561,34 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Qua, semana 14)</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 10C1</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -4602,32 +4598,32 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4639,23 +4635,27 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -4672,27 +4672,27 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
+          <t>11º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4704,296 +4704,284 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 13)</t>
+          <t>6º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 13)</t>
+          <t>2º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
+          <t>9º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr"/>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr"/>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 15)</t>
+          <t>3º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5005,30 +4993,30 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 4)</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr"/>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 11C2</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -5038,27 +5026,27 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 5)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5075,12 +5063,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 5)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -5095,7 +5083,7 @@
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -5112,23 +5100,27 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 8)</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -5145,27 +5137,27 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -5182,30 +5174,30 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr"/>
+          <t>6º tempo(s) (Seg, semana 9)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -5215,27 +5207,27 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
+          <t>1º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -5252,27 +5244,27 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -5289,28 +5281,32 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5322,32 +5318,28 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr"/>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5359,12 +5351,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>9º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -5379,7 +5371,7 @@
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -5396,27 +5388,23 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 8)</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr"/>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -5433,27 +5421,27 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -5470,30 +5458,30 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 9)</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr"/>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 11C2</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -5508,22 +5496,22 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 10)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -5545,22 +5533,22 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>7º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -5577,27 +5565,23 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -5614,28 +5598,32 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Qui, semana 16)</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5647,12 +5635,12 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 14)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -5667,7 +5655,7 @@
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -5684,23 +5672,27 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -5717,27 +5709,27 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5749,124 +5741,124 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Qua, semana 5)</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
+          <t>2º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
+          <t>7º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr"/>
@@ -5877,160 +5869,156 @@
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
+          <t>3º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>2º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6042,27 +6030,27 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 5)</t>
+          <t>9º tempo(s) (Qua, semana 8)</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -6079,23 +6067,27 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 10)</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -6112,34 +6104,30 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
-        </is>
-      </c>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -6149,28 +6137,32 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr"/>
+          <t>1º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6182,32 +6174,28 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6219,28 +6207,28 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6252,27 +6240,27 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>9º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -6289,27 +6277,27 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 8)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
@@ -6326,32 +6314,28 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qua, semana 8)</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr"/>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6368,22 +6352,22 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
@@ -6400,30 +6384,34 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -6433,27 +6421,23 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 12)</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr"/>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
@@ -6470,28 +6454,32 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 16)</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6503,23 +6491,27 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -6531,114 +6523,110 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr"/>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr"/>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
@@ -6648,12 +6636,12 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -6663,104 +6651,100 @@
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>11º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -6770,49 +6754,45 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6824,23 +6804,27 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Qui, semana 6)</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
+        </is>
+      </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -6857,23 +6841,27 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 6)</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
@@ -6890,27 +6878,27 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 4)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -6927,32 +6915,32 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -6964,28 +6952,32 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Ter, semana 7)</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6997,30 +6989,34 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 5)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 12C2</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -7030,27 +7026,27 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -7067,23 +7063,27 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>Fab (Fabio Merçon)</t>
+        </is>
+      </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
@@ -7100,27 +7100,23 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 6)</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr">
-        <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr"/>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -7137,12 +7133,12 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 6)</t>
+          <t>11º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
@@ -7157,7 +7153,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
@@ -7174,27 +7170,27 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -7211,32 +7207,32 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>3º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7248,27 +7244,27 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -7285,32 +7281,28 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr"/>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7322,27 +7314,27 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -7359,32 +7351,32 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7396,23 +7388,27 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
+        </is>
+      </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -7429,27 +7425,27 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -7466,27 +7462,27 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7503,27 +7499,27 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 12)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7535,12 +7531,12 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -7565,262 +7561,250 @@
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr"/>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
+          <t>11º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr"/>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>5º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr"/>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr"/>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7816,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -7857,7 +7841,7 @@
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7869,23 +7853,27 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -7902,27 +7890,27 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -7939,28 +7927,32 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>Isb (Isabela Gomes Bustamante)</t>
+        </is>
+      </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -7972,27 +7964,27 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -8009,32 +8001,32 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8046,28 +8038,32 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8079,23 +8075,27 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
@@ -8112,27 +8112,23 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr"/>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8149,12 +8145,12 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>10º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
@@ -8169,7 +8165,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
@@ -8186,27 +8182,27 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -8223,32 +8219,32 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8260,27 +8256,23 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr"/>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -8297,27 +8289,27 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
@@ -8334,27 +8326,27 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -8371,27 +8363,27 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
@@ -8408,23 +8400,27 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Sex, semana 14)</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -8441,27 +8437,27 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qua, semana 12)</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -8478,12 +8474,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -8498,7 +8494,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -8507,300 +8503,8 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B202" s="6" t="inlineStr">
-        <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
-        </is>
-      </c>
-      <c r="C202" s="5" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D202" s="6" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
-      <c r="E202" s="5" t="inlineStr">
-        <is>
-          <t>Hist</t>
-        </is>
-      </c>
-      <c r="F202" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
-        </is>
-      </c>
-      <c r="G202" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr"/>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>Artes</t>
-        </is>
-      </c>
-      <c r="F203" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
-        </is>
-      </c>
-      <c r="G203" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
-      <c r="C204" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D204" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E204" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F204" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G204" s="6" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="inlineStr">
-        <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>Fis</t>
-        </is>
-      </c>
-      <c r="F205" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
-        </is>
-      </c>
-      <c r="G205" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B206" s="6" t="inlineStr">
-        <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
-      <c r="C206" s="5" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
-        </is>
-      </c>
-      <c r="D206" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E206" s="5" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F206" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
-        </is>
-      </c>
-      <c r="G206" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>Redação</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B208" s="6" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C208" s="5" t="inlineStr">
-        <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D208" s="6" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="E208" s="5" t="inlineStr">
-        <is>
-          <t>Fis</t>
-        </is>
-      </c>
-      <c r="F208" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G208" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C209" s="3" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F209" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G209" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G209"/>
+  <autoFilter ref="A2:G201"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -8814,7 +8518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9476,17 +9180,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9212,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -9569,12 +9273,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -9591,17 +9295,61 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
           <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D36"/>
+  <autoFilter ref="A2:D38"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$202</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1349,27 +1349,23 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 5)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1386,32 +1382,32 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1423,27 +1419,27 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 6)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -1460,32 +1456,32 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1497,27 +1493,27 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
+          <t>10º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1534,23 +1530,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
+          <t>6º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>7º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1641,27 +1641,23 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
-        </is>
-      </c>
+          <t>4º, 5º tempo(s) (Seg, semana 12)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º, 5º de Ed.Física para a prova de Redação</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1937,27 +1933,27 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>5º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1969,37 +1965,37 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 4)</t>
+          <t>4º tempo(s) (Ter, semana 16)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 4º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2016,22 +2012,22 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 4)</t>
+          <t>4º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -2048,27 +2044,27 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -2085,32 +2081,28 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2122,27 +2114,27 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2159,32 +2151,32 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2196,23 +2188,27 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
+          <t>9º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+        </is>
+      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2229,32 +2225,32 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2266,32 +2262,32 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2303,27 +2299,23 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
-        </is>
-      </c>
+          <t>4º, 5º tempo(s) (Seg, semana 12)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º, 5º de Ed.Física para a prova de Redação</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -2562,27 +2554,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>4º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2599,27 +2591,27 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
+          <t>5º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 7º de Hist para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -2631,37 +2623,37 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 4)</t>
+          <t>4º tempo(s) (Ter, semana 16)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2678,22 +2670,22 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>4º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2710,27 +2702,27 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Ter, semana 4)</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2747,32 +2739,32 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>6º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2784,32 +2776,32 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -2826,22 +2818,22 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>1º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -2858,32 +2850,32 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 5)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2887,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>3º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -2915,12 +2907,12 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
@@ -2932,32 +2924,32 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -2969,27 +2961,27 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -3006,23 +2998,27 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -3044,22 +3040,18 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr"/>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -3076,27 +3068,27 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 9)</t>
+          <t>10º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -3113,27 +3105,27 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 10)</t>
+          <t>5º tempo(s) (Sex, semana 9)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -3155,22 +3147,22 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>4º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -3187,12 +3179,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -3207,7 +3199,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -3224,30 +3216,34 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 12)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -3257,34 +3253,30 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>4º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -3294,28 +3286,32 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3332,22 +3328,18 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr"/>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -3364,27 +3356,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 13)</t>
+          <t>10º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3406,22 +3398,22 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
+          <t>1º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -3438,27 +3430,27 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -3475,27 +3467,27 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -3512,27 +3504,27 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 14)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -3554,22 +3546,22 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>10º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -3586,32 +3578,32 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3623,32 +3615,32 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 15)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3665,22 +3657,22 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
+          <t>4º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -3697,27 +3689,27 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3729,37 +3721,37 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3771,27 +3763,27 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -3808,32 +3800,32 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3845,12 +3837,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -3865,12 +3857,12 @@
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -3887,22 +3879,22 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -3919,26 +3911,34 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>FBri (Fábio Luís de Brito)</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -3948,34 +3948,26 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -3985,32 +3977,32 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4022,27 +4014,27 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -4064,22 +4056,22 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -4096,23 +4088,27 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -4129,27 +4125,23 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr"/>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -4166,27 +4158,27 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -4203,27 +4195,27 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -4245,22 +4237,22 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -4277,26 +4269,34 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -4306,34 +4306,26 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr"/>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -4343,28 +4335,32 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4376,27 +4372,23 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr"/>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -4418,22 +4410,22 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 13)</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -4450,27 +4442,27 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 13)</t>
+          <t>3º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -4487,27 +4479,27 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
+          <t>1º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4524,27 +4516,27 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>2º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -4561,32 +4553,32 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4598,32 +4590,32 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4635,27 +4627,27 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -4677,22 +4669,22 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 15)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4704,35 +4696,39 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 4)</t>
+          <t>11º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -4742,34 +4738,30 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 5)</t>
+          <t>6º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -4779,27 +4771,27 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 5)</t>
+          <t>2º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -4821,18 +4813,22 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr"/>
+          <t>9º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -4849,27 +4845,23 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr"/>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -4886,28 +4878,32 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr"/>
+          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4919,32 +4915,28 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr"/>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -4961,22 +4953,22 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -4993,28 +4985,32 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5026,32 +5022,28 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5068,22 +5060,22 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -5100,27 +5092,27 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 8)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -5137,27 +5129,27 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -5174,30 +5166,34 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 9)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -5207,34 +5203,30 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 10)</t>
+          <t>6º tempo(s) (Seg, semana 9)</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -5249,22 +5241,22 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>1º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -5281,12 +5273,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -5301,7 +5293,7 @@
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -5318,28 +5310,32 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5351,32 +5347,28 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr"/>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5393,18 +5385,22 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr"/>
+          <t>9º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -5421,27 +5417,23 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr"/>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -5458,28 +5450,32 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5491,32 +5487,28 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5533,22 +5525,22 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -5565,23 +5557,27 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr"/>
+          <t>7º tempo(s) (Seg, semana 16)</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -5598,27 +5594,23 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -5640,22 +5632,22 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>4º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -5672,27 +5664,27 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -5714,22 +5706,22 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>1º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5741,37 +5733,37 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 5)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5783,23 +5775,27 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr"/>
+          <t>1º tempo(s) (Qua, semana 5)</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -5816,27 +5812,23 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr"/>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -5853,28 +5845,32 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5886,32 +5882,28 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr"/>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -5923,28 +5915,32 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5956,32 +5952,28 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr"/>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -5993,27 +5985,27 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 8)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -6030,27 +6022,27 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qua, semana 8)</t>
+          <t>2º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -6067,27 +6059,27 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>9º tempo(s) (Qua, semana 8)</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -6104,30 +6096,34 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G135" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -6137,34 +6133,30 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 12)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -6174,28 +6166,32 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6207,28 +6203,28 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+          <t>7º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6240,27 +6236,23 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -6282,22 +6274,22 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>9º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
@@ -6314,28 +6306,32 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6347,32 +6343,28 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr"/>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6384,27 +6376,27 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 16)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -6426,18 +6418,22 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
@@ -6454,27 +6450,23 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr"/>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -6491,27 +6483,27 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -6523,33 +6515,37 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6561,23 +6557,23 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr"/>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
@@ -6599,22 +6595,18 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -6631,27 +6623,27 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>3º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
@@ -6668,28 +6660,32 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6701,30 +6697,30 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr"/>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -6734,12 +6730,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
+          <t>5º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -6754,14 +6750,10 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
-        </is>
-      </c>
-      <c r="G153" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -6776,18 +6768,22 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
@@ -6804,27 +6800,23 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 6)</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr"/>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -6846,22 +6838,22 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 6)</t>
+          <t>4º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
@@ -6878,27 +6870,27 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>5º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -6915,12 +6907,12 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
@@ -6935,12 +6927,12 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6952,32 +6944,32 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 7)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -6989,32 +6981,32 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7026,32 +7018,32 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7068,22 +7060,22 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
@@ -7100,23 +7092,27 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>Fab (Fabio Merçon)</t>
+        </is>
+      </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -7138,22 +7134,18 @@
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr"/>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
@@ -7170,27 +7162,27 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -7207,27 +7199,27 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
@@ -7244,27 +7236,27 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -7281,23 +7273,27 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
@@ -7319,22 +7315,18 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr"/>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -7351,32 +7343,32 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7388,32 +7380,32 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7425,27 +7417,27 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -7467,22 +7459,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7499,27 +7491,27 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7531,37 +7523,37 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7573,28 +7565,32 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
@@ -7611,22 +7607,18 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr"/>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -7643,23 +7635,27 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
@@ -7676,27 +7672,23 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr"/>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -7718,22 +7710,22 @@
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
@@ -7750,28 +7742,32 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>Isb (Isabela Gomes Bustamante)</t>
+        </is>
+      </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7783,28 +7779,28 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
+          <t>5º tempo(s) (Ter, semana 5)</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr"/>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -7816,27 +7812,23 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -7853,27 +7845,27 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -7895,22 +7887,22 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -7927,32 +7919,32 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7964,32 +7956,32 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8001,32 +7993,32 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8038,32 +8030,32 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8080,22 +8072,22 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
@@ -8112,23 +8104,27 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8145,27 +8141,23 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qua, semana 12)</t>
-        </is>
-      </c>
-      <c r="D192" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr"/>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
@@ -8182,12 +8174,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
+          <t>10º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -8202,7 +8194,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -8219,27 +8211,27 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
+          <t>2º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
@@ -8256,23 +8248,27 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -8289,32 +8285,28 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D196" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr"/>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8326,32 +8318,32 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8368,22 +8360,22 @@
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
@@ -8400,27 +8392,27 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -8437,27 +8429,27 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -8479,32 +8471,69 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
+          <t>1º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Fis</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>12C2</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
           <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
-      <c r="D201" s="4" t="inlineStr">
+      <c r="D202" s="6" t="inlineStr">
         <is>
           <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
+      <c r="E202" s="5" t="inlineStr">
         <is>
           <t>Port</t>
         </is>
       </c>
-      <c r="F201" s="4" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
-      <c r="G201" s="4" t="inlineStr">
+      <c r="G202" s="6" t="inlineStr">
         <is>
           <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G201"/>
+  <autoFilter ref="A2:G202"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -9180,17 +9209,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 3 (nunca 2 semanas seguidas sem contato)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
+          <t>fica sem contato com a turma nas semanas 11 e 12 por causa das cessões</t>
         </is>
       </c>
     </row>
@@ -9268,17 +9297,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 3 (nunca 2 semanas seguidas sem contato)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
+          <t>fica sem contato com a turma nas semanas 11 e 12 por causa das cessões</t>
         </is>
       </c>
     </row>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$209</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1349,27 +1349,23 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 5)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1386,32 +1382,32 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1423,27 +1419,27 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 6)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -1460,32 +1456,32 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1497,27 +1493,27 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
+          <t>10º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1534,32 +1530,32 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 7)</t>
+          <t>6º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 4º de Hist para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1571,23 +1567,27 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr"/>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Jana (Janaína Souza Silva)</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1604,32 +1604,32 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 1º de Bio para a prova de Redação</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1678,32 +1678,32 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Redação</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1715,27 +1715,27 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 12)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1752,32 +1752,32 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
+          <t>4º tempo(s) (Ter, semana 13)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 4º de Hist para a prova de DaF</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Qui / Fab (Fabio Merçon)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1974,27 +1974,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -2011,106 +2011,106 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Ter, semana 16)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>5º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2122,27 +2122,23 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2159,27 +2155,27 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 4)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -2196,7 +2192,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2221,7 +2217,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2233,32 +2229,32 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2270,27 +2266,27 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 6)</t>
+          <t>6º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -2307,32 +2303,32 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2344,32 +2340,32 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 7)</t>
+          <t>2º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 2º de Fis para a prova de Redação</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2381,23 +2377,27 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -2414,27 +2414,27 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4º tempo(s) (Ter, semana 13)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de DaF</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -2451,32 +2451,32 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2488,32 +2488,32 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2525,27 +2525,27 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 12)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -2562,27 +2562,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2599,27 +2599,27 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 13)</t>
+          <t>4º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -2636,27 +2636,27 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Qui / Fab (Fabio Merçon)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Sex, semana 13)</t>
+          <t>5º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Raf (Rafael Alverne Freitas de Albuquerque) a cessão do(s) tempo(s) 7º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2673,27 +2673,27 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2705,222 +2705,222 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qui, semana 14)</t>
+          <t>4º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>1º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 7º de Hist para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2932,32 +2932,32 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 4)</t>
+          <t>3º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
@@ -2969,32 +2969,32 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3006,27 +3006,27 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Ter, semana 4)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3080,27 +3080,23 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>FBri (Fábio Luís de Brito)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -3117,27 +3113,27 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>10º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -3154,32 +3150,32 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 5)</t>
+          <t>5º tempo(s) (Sex, semana 9)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3191,32 +3187,32 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>4º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3228,27 +3224,27 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -3270,22 +3266,22 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -3302,30 +3298,30 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 12)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>VSi (Vinícius de Paula Silveira)</t>
+        </is>
+      </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -3335,32 +3331,32 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 7)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3372,27 +3368,23 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 9)</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3409,27 +3401,27 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 10)</t>
+          <t>10º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -3446,27 +3438,27 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>1º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -3483,12 +3475,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -3503,7 +3495,7 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -3520,30 +3512,34 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -3553,32 +3549,32 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3590,23 +3586,27 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+        </is>
+      </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -3623,27 +3623,27 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 12)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -3660,32 +3660,32 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 13)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3697,27 +3697,27 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
+          <t>4º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3734,27 +3734,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3771,27 +3771,27 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -3803,44 +3803,44 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 14)</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -3865,162 +3865,154 @@
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 15)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
+          <t>3º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr"/>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -4030,32 +4022,32 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4067,27 +4059,27 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -4104,32 +4096,32 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4141,27 +4133,27 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -4178,27 +4170,23 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>FBri (Fábio Luís de Brito)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr"/>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -4215,26 +4203,34 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -4244,32 +4240,32 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4281,27 +4277,27 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -4323,22 +4319,22 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -4355,34 +4351,26 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr"/>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -4392,28 +4380,32 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4425,27 +4417,23 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr"/>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -4462,12 +4450,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -4482,7 +4470,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -4499,27 +4487,27 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>3º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4536,27 +4524,27 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>1º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -4573,26 +4561,34 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>MFo (Mário Henrique Fonseca)</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -4602,32 +4598,32 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4639,28 +4635,32 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Qua, semana 14)</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4672,27 +4672,27 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4709,27 +4709,27 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 13)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -4746,27 +4746,27 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 13)</t>
+          <t>11º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -4778,222 +4778,210 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
+          <t>6º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>2º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>9º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr"/>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr"/>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5005,30 +4993,34 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 4)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -5038,27 +5030,27 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 5)</t>
+          <t>3º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5075,32 +5067,28 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr"/>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5112,23 +5100,27 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -5145,27 +5137,27 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -5182,28 +5174,32 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 8)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5215,27 +5211,27 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -5252,34 +5248,30 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>6º tempo(s) (Seg, semana 9)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -5289,28 +5281,32 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr"/>
+          <t>1º tempo(s) (Qua, semana 10)</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5322,27 +5318,27 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -5359,27 +5355,27 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -5396,32 +5392,28 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 8)</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr"/>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5433,27 +5425,27 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -5470,30 +5462,30 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 9)</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr"/>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -5503,27 +5495,27 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 10)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -5540,32 +5532,28 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5577,27 +5565,27 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -5614,28 +5602,32 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr"/>
+          <t>7º tempo(s) (Seg, semana 16)</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5647,27 +5639,23 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -5684,23 +5672,27 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Qui, semana 16)</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -5717,27 +5709,27 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5754,28 +5746,32 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5787,27 +5783,27 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -5819,166 +5815,162 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
+          <t>1º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr"/>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
+          <t>2º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr"/>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>3º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -5988,49 +5980,45 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr"/>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6042,27 +6030,27 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 5)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -6079,23 +6067,27 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Seg, semana 8)</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -6112,27 +6104,27 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 6)</t>
+          <t>9º tempo(s) (Qua, semana 8)</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -6149,28 +6141,32 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 10)</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6182,34 +6178,30 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
-        </is>
-      </c>
-      <c r="G137" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -6219,28 +6211,32 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr"/>
+          <t>1º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6252,32 +6248,28 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6289,27 +6281,23 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 8)</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr"/>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
@@ -6326,27 +6314,27 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qua, semana 8)</t>
+          <t>9º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -6363,12 +6351,12 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -6383,7 +6371,7 @@
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
@@ -6400,30 +6388,30 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 11C1</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -6433,27 +6421,27 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 12)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
@@ -6470,28 +6458,32 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6503,23 +6495,23 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+          <t>3º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -6536,27 +6528,27 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -6573,27 +6565,27 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
@@ -6605,17 +6597,17 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr"/>
@@ -6626,195 +6618,187 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 16)</t>
+          <t>3º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr"/>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>5º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -6824,23 +6808,27 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -6857,23 +6845,23 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
+          <t>12º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
@@ -6890,27 +6878,27 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 4)</t>
+          <t>4º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -6927,27 +6915,27 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
@@ -6964,28 +6952,32 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6997,30 +6989,34 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 5)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 12C2</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -7030,27 +7026,27 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
+          <t>3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -7067,28 +7063,32 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Qui, semana 9)</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7100,27 +7100,27 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -7137,27 +7137,27 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
@@ -7174,27 +7174,23 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr"/>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -7211,32 +7207,32 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>11º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7248,27 +7244,27 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -7285,32 +7281,32 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>3º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7322,27 +7318,27 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -7359,27 +7355,23 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
-        <is>
-          <t>Fab (Fabio Merçon)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr"/>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
@@ -7396,23 +7388,27 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -7429,32 +7425,32 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7466,27 +7462,27 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7503,27 +7499,27 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 12)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7540,27 +7536,27 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -7577,23 +7573,27 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
@@ -7605,222 +7605,214 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr"/>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>11º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr"/>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7832,32 +7824,28 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -7869,23 +7857,23 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+          <t>12º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr"/>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -7902,27 +7890,27 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -7939,23 +7927,27 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
@@ -7972,27 +7964,27 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -8009,12 +8001,12 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
@@ -8029,12 +8021,12 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8046,28 +8038,32 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 7)</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8079,28 +8075,32 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Qui, semana 9)</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8112,27 +8112,27 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8149,27 +8149,27 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
@@ -8186,27 +8186,23 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr"/>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -8223,32 +8219,32 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>10º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8260,12 +8256,12 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>2º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -8280,7 +8276,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -8297,32 +8293,32 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>2º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8334,27 +8330,23 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr"/>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -8371,32 +8363,32 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8408,23 +8400,27 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -8441,12 +8437,12 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qua, semana 12)</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
@@ -8461,7 +8457,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -8478,27 +8474,27 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -8515,27 +8511,27 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
@@ -8552,23 +8548,27 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -8577,230 +8577,8 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
-      <c r="C204" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D204" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E204" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F204" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G204" s="6" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="inlineStr">
-        <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>Fis</t>
-        </is>
-      </c>
-      <c r="F205" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
-        </is>
-      </c>
-      <c r="G205" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B206" s="6" t="inlineStr">
-        <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
-      <c r="C206" s="5" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
-        </is>
-      </c>
-      <c r="D206" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E206" s="5" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F206" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
-        </is>
-      </c>
-      <c r="G206" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>Redação</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B208" s="6" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C208" s="5" t="inlineStr">
-        <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D208" s="6" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="E208" s="5" t="inlineStr">
-        <is>
-          <t>Fis</t>
-        </is>
-      </c>
-      <c r="F208" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G208" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C209" s="3" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F209" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G209" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G209"/>
+  <autoFilter ref="A2:G203"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -8814,7 +8592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9508,7 +9286,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9303,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9337,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -9569,12 +9347,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9586,22 +9364,88 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>Regra 3 (nunca 2 semanas seguidas sem contato)</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>fica sem contato com a turma nas semanas 11 e 12 por causa das cessões</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
           <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D36"/>
+  <autoFilter ref="A2:D39"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$203</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1641,27 +1641,27 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 12)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 1º de Bio para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1683,22 +1683,18 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 12)</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1715,12 +1711,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
+          <t>5º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1735,7 +1731,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -2340,27 +2336,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 2º de Fis para a prova de Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -2377,27 +2373,23 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -8592,7 +8584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9303,12 +9295,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9329,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -9347,12 +9339,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -9364,17 +9356,17 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Regra 3 (nunca 2 semanas seguidas sem contato)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>fica sem contato com a turma nas semanas 11 e 12 por causa das cessões</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
@@ -9391,61 +9383,17 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
           <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D39"/>
+  <autoFilter ref="A2:D37"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$203</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G203"/>
+  <dimension ref="A1:G206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1604,32 +1604,32 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1641,27 +1641,27 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Bio</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1678,28 +1678,32 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1715,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 12)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1731,7 +1735,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1748,32 +1752,28 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 13)</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 4º de Hist para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1785,27 +1785,27 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 13)</t>
+          <t>5º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 5º de Mat para a prova de Redação</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1822,32 +1822,32 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
+          <t>4º tempo(s) (Ter, semana 13)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 4º de Hist para a prova de DaF</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1896,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -2007,86 +2007,86 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 16)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 4)</t>
+          <t>1º tempo(s) (Ter, semana 16)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Ter, semana 16)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -2101,45 +2101,49 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Bio</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2151,27 +2155,27 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -2188,32 +2192,32 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2225,27 +2229,23 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -2262,27 +2262,27 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -2336,27 +2336,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -2373,23 +2373,27 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
+          <t>6º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -2406,32 +2410,32 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 13)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Bio</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2443,32 +2447,32 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2484,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2505,7 +2509,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2517,27 +2521,23 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 14)</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Jana (Janaína Souza Silva)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qui, semana 14)</t>
+          <t>4º tempo(s) (Ter, semana 13)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de DaF</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2591,27 +2591,27 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 15)</t>
+          <t>6º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -2628,27 +2628,27 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 15)</t>
+          <t>7º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2665,27 +2665,27 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2697,148 +2697,148 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 4)</t>
+          <t>5º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Ter, semana 16)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Bio</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2850,27 +2850,27 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 5)</t>
+          <t>4º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -2887,27 +2887,27 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -2924,32 +2924,32 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 5)</t>
+          <t>6º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2961,27 +2961,27 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -2998,27 +2998,27 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
+          <t>1º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -3035,27 +3035,27 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -3072,28 +3072,32 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Qua, semana 5)</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3109,32 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 7)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3142,27 +3146,27 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 9)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -3179,27 +3183,27 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 10)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -3216,27 +3220,23 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -3253,27 +3253,27 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>10º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -3290,30 +3290,34 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 12)</t>
+          <t>5º tempo(s) (Sex, semana 9)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -3323,32 +3327,32 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>4º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3360,23 +3364,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 10)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3393,27 +3401,27 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 12)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -3430,34 +3438,30 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 13)</t>
+          <t>4º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -3467,12 +3471,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -3487,12 +3491,12 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3504,27 +3508,23 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -3541,27 +3541,27 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
+          <t>10º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -3578,27 +3578,27 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 14)</t>
+          <t>1º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -3615,27 +3615,27 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3689,27 +3689,27 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 15)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3726,27 +3726,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
+          <t>10º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -3795,148 +3795,148 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
+          <t>4º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3948,27 +3948,27 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -3985,26 +3985,34 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr"/>
+          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -4014,27 +4022,27 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -4051,27 +4059,27 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -4088,27 +4096,27 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -4125,34 +4133,26 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr"/>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -4162,28 +4162,32 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4195,27 +4199,27 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -4232,27 +4236,27 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -4274,7 +4278,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -4306,27 +4310,23 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr"/>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -4343,26 +4343,34 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -4372,12 +4380,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -4392,12 +4400,12 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4409,23 +4417,27 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -4442,12 +4454,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -4462,7 +4474,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -4479,34 +4491,26 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 13)</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>FBri (Fábio Luís de Brito)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr"/>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -4516,32 +4520,32 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 13)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4553,27 +4557,23 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr"/>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -4590,27 +4590,27 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -4627,32 +4627,32 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>3º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4664,27 +4664,27 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
+          <t>1º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4701,27 +4701,27 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 15)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -4770,140 +4770,148 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 4)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 10C1</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 5)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 5)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+        </is>
+      </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4915,34 +4923,30 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
+          <t>6º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -4952,28 +4956,32 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 5)</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4985,27 +4993,27 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
+          <t>9º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -5022,27 +5030,23 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5059,28 +5063,32 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr"/>
+          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5092,32 +5100,28 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5129,27 +5133,27 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -5166,12 +5170,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 8)</t>
+          <t>3º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -5186,7 +5190,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -5203,32 +5207,28 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr"/>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5240,30 +5240,34 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 9)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -5273,27 +5277,27 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 10)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -5310,27 +5314,27 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>3º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -5347,27 +5351,27 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -5384,30 +5388,30 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr"/>
+          <t>6º tempo(s) (Seg, semana 9)</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -5417,27 +5421,27 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 14)</t>
+          <t>1º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -5454,23 +5458,27 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 10)</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -5487,27 +5495,27 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -5524,12 +5532,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
+          <t>7º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr"/>
@@ -5540,7 +5548,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -5557,27 +5565,27 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>9º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
@@ -5594,27 +5602,23 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -5631,23 +5635,27 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -5664,32 +5672,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr"/>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5701,27 +5705,27 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -5738,27 +5742,27 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>7º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -5775,27 +5779,23 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr"/>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -5807,77 +5807,81 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 5)</t>
+          <t>4º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 16)</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -5887,7 +5891,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 6)</t>
+          <t>1º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -5902,45 +5906,49 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5952,27 +5960,27 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>1º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -5989,28 +5997,28 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr"/>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6022,27 +6030,27 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>2º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -6059,32 +6067,28 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 8)</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6096,27 +6100,27 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qua, semana 8)</t>
+          <t>3º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -6133,32 +6137,28 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6170,30 +6170,34 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G137" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -6203,27 +6207,27 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 12)</t>
+          <t>2º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -6240,28 +6244,32 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr"/>
+          <t>9º tempo(s) (Qua, semana 8)</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6273,23 +6281,27 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 10)</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
@@ -6306,34 +6318,30 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
-        </is>
-      </c>
-      <c r="G141" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -6343,27 +6351,27 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>1º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G142" s="6" t="inlineStr">
@@ -6380,12 +6388,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
+          <t>7º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr"/>
@@ -6396,7 +6404,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -6413,27 +6421,23 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr"/>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
@@ -6450,27 +6454,27 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 16)</t>
+          <t>9º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -6487,23 +6491,27 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -6520,32 +6528,28 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr"/>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6557,27 +6561,27 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
@@ -6589,73 +6593,77 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
+          <t>3º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr"/>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -6665,7 +6673,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 4)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -6675,54 +6683,54 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6734,12 +6742,12 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr"/>
@@ -6750,12 +6758,12 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6767,30 +6775,30 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -6800,27 +6808,27 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
+          <t>3º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -6837,23 +6845,27 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
@@ -6870,32 +6882,28 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 6)</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr"/>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -6907,12 +6915,12 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 6)</t>
+          <t>11º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
@@ -6927,7 +6935,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
@@ -6944,27 +6952,23 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr"/>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -6981,32 +6985,32 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>4º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7018,27 +7022,27 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 7)</t>
+          <t>5º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -7055,32 +7059,32 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7092,12 +7096,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -7112,12 +7116,12 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7129,27 +7133,27 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
@@ -7166,28 +7170,32 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Qui, semana 9)</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7199,27 +7207,27 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
@@ -7236,27 +7244,27 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -7273,27 +7281,23 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 12)</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
-        <is>
-          <t>Fab (Fabio Merçon)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr"/>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
@@ -7310,27 +7314,27 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -7347,23 +7351,27 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
@@ -7380,27 +7388,27 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
+          <t>3º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -7417,7 +7425,7 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
@@ -7442,7 +7450,7 @@
       </c>
       <c r="G172" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7454,27 +7462,23 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr"/>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7491,27 +7495,27 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7528,32 +7532,32 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7565,27 +7569,27 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
@@ -7597,107 +7601,111 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Sex, semana 14)</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7709,28 +7717,32 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
@@ -7742,27 +7754,23 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr"/>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -7779,27 +7787,27 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
+          <t>11º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
@@ -7816,28 +7824,28 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
+          <t>2º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7849,23 +7857,27 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -7882,27 +7894,27 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -7919,32 +7931,28 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr"/>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -7956,27 +7964,23 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr"/>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -7993,32 +7997,32 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8030,12 +8034,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -8050,7 +8054,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -8067,32 +8071,32 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8104,32 +8108,32 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8141,27 +8145,27 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
@@ -8178,28 +8182,32 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Qui, semana 9)</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8211,27 +8219,27 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qua, semana 12)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
@@ -8248,27 +8256,27 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -8285,27 +8293,23 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D196" s="6" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr"/>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
@@ -8322,23 +8326,27 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -8355,32 +8363,32 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8392,27 +8400,27 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>2º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -8429,27 +8437,23 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
-        </is>
-      </c>
-      <c r="D200" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr"/>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -8466,32 +8470,32 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8503,12 +8507,12 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -8523,7 +8527,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
@@ -8540,37 +8544,148 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>2º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>12C2</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>4º tempo(s) (Sex, semana 14)</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>Redação</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>12C2</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
           <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
-      <c r="C203" s="3" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>1º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>Fis</t>
+        </is>
+      </c>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>12C2</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
         <is>
           <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
-      <c r="D203" s="4" t="inlineStr">
+      <c r="D206" s="6" t="inlineStr">
         <is>
           <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
-      <c r="E203" s="3" t="inlineStr">
+      <c r="E206" s="5" t="inlineStr">
         <is>
           <t>Port</t>
         </is>
       </c>
-      <c r="F203" s="4" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
-      <c r="G203" s="4" t="inlineStr">
+      <c r="G206" s="6" t="inlineStr">
         <is>
           <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G203"/>
+  <autoFilter ref="A2:G206"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -8584,7 +8699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9256,7 +9371,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9388,12 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 13</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9427,17 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9339,61 +9454,17 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>cedeu aula na semana 14 tendo prova própria na semana 14</t>
+          <t>cedeu aula na semana 15 tendo prova própria na semana 16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D37"/>
+  <autoFilter ref="A2:D35"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$206</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G206"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 4)</t>
+          <t>4º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 4)</t>
+          <t>5º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1419,32 +1419,32 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 5)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º, 5º de Mat para a prova de Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C2</t>
         </is>
       </c>
     </row>
@@ -1456,32 +1456,32 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Port</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C2</t>
+          <t>Prova conjunta com 9C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -1493,27 +1493,27 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 6)</t>
+          <t>6º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 6)</t>
+          <t>7º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
+          <t>1º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 7º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1609,22 +1609,22 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 7)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 1º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Bio</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1641,27 +1641,27 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 4)</t>
+          <t>4º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 1º de Bio para a prova de Port</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2336,27 +2336,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 6)</t>
+          <t>2º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JuLa (Júlia Soares Leite Lanzarini de Carvalho) a cessão do(s) tempo(s) 9º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Port</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -2447,32 +2447,32 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4º, 5º tempo(s) (Qua, semana 7)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia), PaH (Paulo Henrique Sá Júnior), Velo (Rodrigo Veloso)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2521,23 +2521,27 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -2554,32 +2558,28 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>Redação / Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 13)</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Redação</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2591,32 +2591,32 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>DaF / Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Qua, semana 13)</t>
+          <t>4º tempo(s) (Ter, semana 13)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de DaF</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2628,27 +2628,27 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qui, semana 14)</t>
+          <t>6º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 6º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 15)</t>
+          <t>7º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 7º de Mat para a prova de Fis</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 15)</t>
+          <t>4º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 4º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2739,32 +2739,32 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / JuLa (Júlia Soares Leite Lanzarini de Carvalho)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Hist</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 9C1</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2776,32 +2776,32 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / Caro (Carolina Salles Kehl), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 16)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 9C1</t>
         </is>
       </c>
     </row>
@@ -2813,27 +2813,27 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>4º, 5º tempo(s) (Qua, semana 16)</t>
+          <t>2º tempo(s) (Ter, semana 16)</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Jana (Janaína Souza Silva)</t>
+          <t>Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira)</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Caro (Carolina Salles Kehl), SGa (Sabrina Gab), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de Bio</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -2845,37 +2845,37 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 4)</t>
+          <t>4º, 5º tempo(s) (Qua, semana 16)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Jana (Janaína Souza Silva) a cessão do(s) tempo(s) 4º, 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 9C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2892,22 +2892,22 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>4º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -2924,27 +2924,27 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Ter, semana 4)</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -2961,32 +2961,32 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>6º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 6º de Qui para a prova de Bio</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -2998,32 +2998,32 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3040,22 +3040,22 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>1º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -3072,32 +3072,32 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 5)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>3º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
@@ -3146,32 +3146,32 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3183,27 +3183,27 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -3220,23 +3220,27 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -3258,22 +3262,18 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr"/>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -3290,27 +3290,27 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 9)</t>
+          <t>10º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3327,27 +3327,27 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 10)</t>
+          <t>5º tempo(s) (Sex, semana 9)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -3369,22 +3369,22 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>4º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -3438,30 +3438,34 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 12)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -3471,34 +3475,30 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>4º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -3508,28 +3508,32 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3546,22 +3550,18 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr"/>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -3578,27 +3578,27 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 13)</t>
+          <t>10º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -3620,22 +3620,22 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
+          <t>1º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -3652,27 +3652,27 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -3689,27 +3689,27 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3726,27 +3726,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 14)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3768,22 +3768,22 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>10º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -3800,32 +3800,32 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3837,32 +3837,32 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 15)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3879,22 +3879,22 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
+          <t>4º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -3911,27 +3911,27 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
@@ -3943,37 +3943,37 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>10C1</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3985,27 +3985,27 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -4022,32 +4022,32 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4059,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4101,22 +4101,22 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -4133,26 +4133,34 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>FBri (Fábio Luís de Brito)</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -4162,34 +4170,26 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr"/>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -4199,32 +4199,32 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4236,27 +4236,27 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -4310,23 +4310,27 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+        </is>
+      </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -4343,27 +4347,23 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr"/>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -4380,27 +4380,27 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -4417,27 +4417,27 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -4459,22 +4459,22 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -4491,26 +4491,34 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -4520,34 +4528,26 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr"/>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -4557,28 +4557,32 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4590,27 +4594,23 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 13)</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -4664,27 +4664,27 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 13)</t>
+          <t>3º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4701,27 +4701,27 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
+          <t>1º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -4738,27 +4738,27 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>2º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -4775,32 +4775,32 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4812,32 +4812,32 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4849,27 +4849,27 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -4891,22 +4891,22 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 15)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -4918,35 +4918,39 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 4)</t>
+          <t>11º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -4956,34 +4960,30 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 5)</t>
+          <t>6º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
-        </is>
-      </c>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -4993,27 +4993,27 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 5)</t>
+          <t>2º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -5035,18 +5035,22 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr"/>
+          <t>9º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5063,27 +5067,23 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr"/>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -5100,28 +5100,32 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr"/>
+          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5133,32 +5137,28 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr"/>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -5207,28 +5207,32 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5240,32 +5244,28 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr"/>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5282,22 +5282,22 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -5314,27 +5314,27 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 8)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -5351,27 +5351,27 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
@@ -5388,30 +5388,34 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 9)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -5421,34 +5425,30 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 10)</t>
+          <t>6º tempo(s) (Seg, semana 9)</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -5463,22 +5463,22 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>1º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -5532,28 +5532,32 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5565,32 +5569,28 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5607,18 +5607,22 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr"/>
+          <t>9º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -5635,27 +5639,23 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -5672,28 +5672,32 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5705,32 +5709,28 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr"/>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5747,22 +5747,22 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -5779,23 +5779,27 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr"/>
+          <t>7º tempo(s) (Seg, semana 16)</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -5812,27 +5816,23 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr"/>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -5854,22 +5854,22 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>4º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -5886,27 +5886,27 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>1º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -5955,37 +5955,37 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 5)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5997,23 +5997,27 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr"/>
+          <t>1º tempo(s) (Qua, semana 5)</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -6030,27 +6034,23 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -6067,28 +6067,32 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6100,32 +6104,28 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr"/>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6137,28 +6137,32 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6170,32 +6174,28 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6207,27 +6207,27 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 8)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -6244,27 +6244,27 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qua, semana 8)</t>
+          <t>2º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -6281,27 +6281,27 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>9º tempo(s) (Qua, semana 8)</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
         </is>
       </c>
       <c r="G140" s="6" t="inlineStr">
@@ -6318,30 +6318,34 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G141" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -6351,34 +6355,30 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 12)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -6388,28 +6388,32 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr"/>
+          <t>1º tempo(s) (Qua, semana 12)</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6421,28 +6425,28 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+          <t>7º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr"/>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6454,27 +6458,23 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr"/>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -6496,22 +6496,22 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>9º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
@@ -6528,28 +6528,32 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6561,32 +6565,28 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr"/>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6598,27 +6598,27 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 16)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -6640,18 +6640,22 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
@@ -6668,27 +6672,23 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -6705,27 +6705,27 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
@@ -6737,33 +6737,37 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6775,23 +6779,23 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr"/>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
@@ -6813,22 +6817,18 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr"/>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -6845,27 +6845,27 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>3º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
@@ -6882,28 +6882,32 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6915,32 +6919,28 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -6957,18 +6957,22 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -6985,27 +6989,23 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 6)</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr">
-        <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr"/>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
@@ -7027,22 +7027,22 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 6)</t>
+          <t>4º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -7059,27 +7059,27 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>5º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7133,32 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 7)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7170,32 +7170,32 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7207,32 +7207,32 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7249,22 +7249,22 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -7281,23 +7281,27 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>Fab (Fabio Merçon)</t>
+        </is>
+      </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
@@ -7319,22 +7323,18 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr"/>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -7351,27 +7351,27 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
@@ -7388,27 +7388,27 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -7425,27 +7425,27 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -7462,23 +7462,27 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7500,22 +7504,18 @@
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D174" s="6" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr"/>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7569,32 +7569,32 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7606,27 +7606,27 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
@@ -7680,27 +7680,27 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
+          <t>5º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -7712,37 +7712,37 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7754,28 +7754,32 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
@@ -7792,22 +7796,18 @@
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr"/>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
@@ -7824,23 +7824,27 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="inlineStr"/>
+          <t>11º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -7857,27 +7861,23 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr"/>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -7899,22 +7899,22 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -7931,28 +7931,32 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>Isb (Isabela Gomes Bustamante)</t>
+        </is>
+      </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7964,28 +7968,28 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
+          <t>5º tempo(s) (Ter, semana 5)</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr"/>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -7997,27 +8001,23 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr"/>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
@@ -8034,27 +8034,27 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -8076,22 +8076,22 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
@@ -8108,32 +8108,32 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8145,32 +8145,32 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8182,32 +8182,32 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8219,32 +8219,32 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8261,22 +8261,22 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -8293,23 +8293,27 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D196" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Sex, semana 10)</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
@@ -8326,27 +8330,23 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qua, semana 12)</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr"/>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
+          <t>10º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
@@ -8400,27 +8400,27 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
+          <t>2º tempo(s) (Sex, semana 12)</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -8437,23 +8437,27 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D200" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -8470,32 +8474,28 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr"/>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8507,32 +8507,32 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8549,22 +8549,22 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -8581,27 +8581,27 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
@@ -8618,27 +8618,27 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -8660,32 +8660,69 @@
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
+          <t>1º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>Fis</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>12C2</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
           <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
-      <c r="D206" s="6" t="inlineStr">
+      <c r="D207" s="4" t="inlineStr">
         <is>
           <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
-      <c r="E206" s="5" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>Port</t>
         </is>
       </c>
-      <c r="F206" s="6" t="inlineStr">
+      <c r="F207" s="4" t="inlineStr">
         <is>
           <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
-      <c r="G206" s="6" t="inlineStr">
+      <c r="G207" s="4" t="inlineStr">
         <is>
           <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G206"/>
+  <autoFilter ref="A2:G207"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -8699,7 +8736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9388,12 +9425,12 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -9405,29 +9442,29 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -9437,7 +9474,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9454,17 +9491,61 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
           <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>cedeu aula na semana 15 tendo prova própria na semana 16</t>
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Port / Jana (Janaína Souza Silva)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D35"/>
+  <autoFilter ref="A2:D37"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$207</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7425,27 +7425,27 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -7462,27 +7462,23 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr"/>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -7504,18 +7500,22 @@
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D174" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7569,32 +7569,32 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7606,27 +7606,27 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>5º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
@@ -7680,32 +7680,32 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8400,27 +8400,27 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -8437,27 +8437,23 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D200" s="6" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr"/>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -8474,28 +8470,32 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8507,32 +8507,32 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8549,22 +8549,22 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -8581,27 +8581,27 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
@@ -8618,32 +8618,32 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>5º, 6º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º, 6º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9393,7 +9393,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -9452,19 +9452,19 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>9C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
@@ -9486,17 +9486,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9513,12 +9513,12 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 15 tendo prova própria na semana 16</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
@@ -9530,22 +9530,44 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>cedeu aula na semana 15 tendo prova própria na semana 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>9C2</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
           <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D37"/>
+  <autoFilter ref="A2:D38"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$207</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 5)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de Ing</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3146,32 +3146,32 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3183,27 +3183,27 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 6)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -3220,27 +3220,23 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -3262,18 +3258,22 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr"/>
+          <t>10º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -3290,27 +3290,27 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 7)</t>
+          <t>5º tempo(s) (Sex, semana 9)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3327,27 +3327,27 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 9)</t>
+          <t>4º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 5º de Qui para a prova de Soc</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -3369,22 +3369,22 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 10)</t>
+          <t>5º tempo(s) (Qui, semana 10)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 4º de Geo para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3475,30 +3475,30 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 12)</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 12)</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr"/>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -3508,32 +3508,32 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>10º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3545,23 +3545,27 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr"/>
+          <t>1º tempo(s) (Seg, semana 13)</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>FBri (Fábio Luís de Brito)</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -3578,27 +3582,27 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 12)</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 10º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -3615,27 +3619,27 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Seg, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 1º de Mat para a prova de LP/LIT/RED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -3652,27 +3656,27 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
+          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -3689,27 +3693,27 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3726,27 +3730,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Qui, semana 13)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 2º, 3º de Ing para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3763,32 +3767,32 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 14)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C2</t>
         </is>
       </c>
     </row>
@@ -3800,27 +3804,27 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 11º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -3837,32 +3841,32 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C2</t>
+          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3874,27 +3878,27 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 15)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>VSi (Vinícius de Paula Silveira)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). VSi (Vinícius de Paula Silveira) a cessão do(s) tempo(s) 4º de Fis para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -3906,7 +3910,7 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -3916,64 +3920,64 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
+          <t>5º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). APa (Ana Patricia Machado de Pinho Garcia) a cessão do(s) tempo(s) 5º de Ing para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 10º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -3985,32 +3989,32 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 4)</t>
+          <t>2º tempo(s) (Qua, semana 4)</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4022,27 +4026,27 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>6º, 7º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>BrSa (Bruno Vianna dos Santos)</t>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BrSa (Bruno Vianna dos Santos) a cessão do(s) tempo(s) 6º, 7º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -4059,32 +4063,32 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 4)</t>
+          <t>3º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4096,34 +4100,26 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -4133,32 +4129,32 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 5)</t>
+          <t>3º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4170,26 +4166,34 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qui, semana 6)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>MFo (Mário Henrique Fonseca)</t>
+        </is>
+      </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -4199,12 +4203,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 6)</t>
+          <t>1º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -4219,12 +4223,12 @@
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4236,27 +4240,27 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -4273,27 +4277,23 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 6)</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>9º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr"/>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 1º de GL para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -4310,27 +4310,27 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -4347,23 +4347,27 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 10)</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -4380,27 +4384,27 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -4417,12 +4421,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 10)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -4437,7 +4441,7 @@
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 5º de DaF para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -4454,34 +4458,26 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>Vir (Virgínia Granadeiro Chaves Silva)</t>
-        </is>
-      </c>
+          <t>4º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr"/>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Vir (Virgínia Granadeiro Chaves Silva) a cessão do(s) tempo(s) 2º de Ing para a prova de Geo</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -4491,12 +4487,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -4511,12 +4507,12 @@
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4528,26 +4524,30 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Ing / Vir (Virgínia Granadeiro Chaves Silva)</t>
+          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Ter, semana 12)</t>
+          <t>9º tempo(s) (Qui, semana 12)</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr"/>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 4º de Artes para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>2º tempo(s) (Seg, semana 13)</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4594,23 +4594,27 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 12)</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 13)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>FBri (Fábio Luís de Brito)</t>
+        </is>
+      </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º de Ed.Física para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -4627,27 +4631,27 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 13)</t>
+          <t>1º tempo(s) (Qua, semana 13)</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 2º de DaF para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -4664,27 +4668,27 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / BPad (Beatriz de Matos Ferreira Padrão), MFo (Mário Henrique Fonseca), SMo (Samara Costa Moura)</t>
+          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 13)</t>
+          <t>2º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>FBri (Fábio Luís de Brito)</t>
+          <t>MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). FBri (Fábio Luís de Brito) a cessão do(s) tempo(s) 3º de Mat para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4701,27 +4705,27 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 13)</t>
+          <t>11º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Mlo (Marcelo Rios Lopes)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mlo (Marcelo Rios Lopes) a cessão do(s) tempo(s) 1º de Geo para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -4738,32 +4742,32 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Hist / ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
+          <t>3º tempo(s) (Qua, semana 14)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>MFo (Mário Henrique Fonseca)</t>
+          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). MFo (Mário Henrique Fonseca) a cessão do(s) tempo(s) 2º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 10C1</t>
         </is>
       </c>
     </row>
@@ -4775,27 +4779,27 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Bio / Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 14)</t>
+          <t>5º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -4812,32 +4816,32 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 14)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Lza (Luiza Maria Abreu de Mattos)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 3º de GL para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 10C1</t>
+          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4849,27 +4853,27 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 15)</t>
+          <t>11º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). BPad (Beatriz de Matos Ferreira Padrão) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -4881,74 +4885,70 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>6º tempo(s) (Seg, semana 4)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Lza (Luiza Maria Abreu de Mattos)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Lza (Luiza Maria Abreu de Mattos) a cessão do(s) tempo(s) 10º de Bio para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos), FBri (Fábio Luís de Brito)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 15)</t>
+          <t>2º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>ALu (Ana Lúcia Fonseca de Castro)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ALu (Ana Lúcia Fonseca de Castro) a cessão do(s) tempo(s) 11º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 10C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -4960,30 +4960,34 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 4)</t>
+          <t>9º tempo(s) (Qui, semana 5)</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G103" s="4" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -4993,27 +4997,23 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 5)</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr"/>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -5030,27 +5030,27 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 5)</t>
+          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5067,28 +5067,28 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+          <t>7º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr"/>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5100,27 +5100,27 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>2º, 3º tempo(s) (Ter, semana 6)</t>
+          <t>2º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º, 3º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -5137,28 +5137,32 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Mar (Marcelo Alonso Morais)</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5170,32 +5174,28 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5207,27 +5207,27 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>4º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -5244,28 +5244,32 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 7)</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5277,27 +5281,27 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 7)</t>
+          <t>3º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -5314,27 +5318,27 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -5351,34 +5355,30 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 8)</t>
+          <t>6º tempo(s) (Seg, semana 9)</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -5388,27 +5388,27 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -5425,30 +5425,34 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Ing / Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 9)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -5458,27 +5462,27 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 10)</t>
+          <t>2º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 1º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -5495,32 +5499,28 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr"/>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5532,27 +5532,27 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
+          <t>9º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -5569,28 +5569,28 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5602,27 +5602,27 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qui, semana 14)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 9º de Ing para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -5639,28 +5639,28 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+          <t>5º tempo(s) (Qua, semana 15)</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5672,27 +5672,27 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 10º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -5709,28 +5709,32 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr"/>
+          <t>7º tempo(s) (Seg, semana 16)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5742,27 +5746,23 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr"/>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -5779,27 +5779,27 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Seg, semana 16)</t>
+          <t>4º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 7º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -5816,23 +5816,27 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 16)</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+        </is>
+      </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -5849,27 +5853,27 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 16)</t>
+          <t>1º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -5886,27 +5890,27 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
+          <t>2º tempo(s) (Ter, semana 17)</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Bea (Beatriz Souza Andrade Maciel)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bea (Beatriz Souza Andrade Maciel) a cessão do(s) tempo(s) 5º de Ing para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -5918,74 +5922,70 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 17)</t>
+          <t>1º tempo(s) (Qua, semana 5)</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 1º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr"/>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5997,27 +5997,27 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 5)</t>
+          <t>2º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -6034,28 +6034,28 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+          <t>7º tempo(s) (Qua, semana 6)</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6067,17 +6067,17 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 6)</t>
+          <t>3º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
+          <t>5º tempo(s) (Qua, semana 7)</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr"/>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -6137,27 +6137,27 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
@@ -6174,28 +6174,32 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Seg, semana 8)</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
+        </is>
+      </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6207,27 +6211,27 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
+          <t>9º tempo(s) (Qua, semana 8)</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -6244,27 +6248,27 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 8)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -6281,34 +6285,30 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qua, semana 8)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -6318,27 +6318,27 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>1º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -6355,30 +6355,30 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr"/>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>Grupo paralelo já combinado com 11C1</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -6388,27 +6388,23 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 12)</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -6425,28 +6421,32 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr"/>
+          <t>9º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6458,23 +6458,27 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr"/>
+          <t>10º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -6491,32 +6495,28 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 15)</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr"/>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6528,27 +6528,27 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
+          <t>6º tempo(s) (Seg, semana 16)</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -6565,28 +6565,32 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>Ver (Verena Alberti)</t>
+        </is>
+      </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
         </is>
       </c>
       <c r="G148" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6598,27 +6602,23 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
-        </is>
-      </c>
+          <t>3º tempo(s) (Qua, semana 16)</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -6635,27 +6635,27 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 16)</t>
+          <t>5º tempo(s) (Qui, semana 16)</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
@@ -6672,23 +6672,27 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qua, semana 16)</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 17)</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 3º de Aprof. para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -6700,74 +6704,66 @@
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 16)</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr"/>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G152" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 17)</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr"/>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6779,23 +6775,27 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr"/>
+          <t>3º tempo(s) (Qui, semana 4)</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>AMu (André Barros Mucci)</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G154" s="6" t="inlineStr">
@@ -6812,23 +6812,27 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr"/>
+          <t>4º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+        </is>
+      </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -6845,32 +6849,28 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr"/>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G156" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -6882,27 +6882,27 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
+          <t>11º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -6919,28 +6919,28 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
+          <t>12º tempo(s) (Ter, semana 6)</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6952,27 +6952,27 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 6)</t>
+          <t>4º tempo(s) (Qui, semana 6)</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -6989,23 +6989,27 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Qui, semana 6)</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G160" s="6" t="inlineStr">
@@ -7022,27 +7026,27 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Qui, semana 6)</t>
+          <t>2º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). PaH (Paulo Henrique Sá Júnior) a cessão do(s) tempo(s) 4º de Ing para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -7059,32 +7063,32 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 5º de Port para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7096,27 +7100,27 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>3º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -7133,27 +7137,27 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 5º de Geo para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G164" s="6" t="inlineStr">
@@ -7170,27 +7174,27 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Ter, semana 7)</t>
+          <t>2º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 3º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -7207,32 +7211,32 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7244,27 +7248,23 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr"/>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 2º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -7281,27 +7281,27 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>11º tempo(s) (Ter, semana 12)</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Fab (Fabio Merçon)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Qui</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Fab (Fabio Merçon) a cessão do(s) tempo(s) 3º de Qui para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
@@ -7318,23 +7318,27 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -7351,27 +7355,27 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 12)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 11º de Port para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G170" s="6" t="inlineStr">
@@ -7388,27 +7392,23 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr"/>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -7425,27 +7425,27 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Qui, semana 13)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
         </is>
       </c>
       <c r="G172" s="6" t="inlineStr">
@@ -7462,28 +7462,32 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C2</t>
         </is>
       </c>
     </row>
@@ -7495,27 +7499,27 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Qui, semana 13)</t>
+          <t>1º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 3º de Redação para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7532,32 +7536,32 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C2</t>
+          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7569,27 +7573,27 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>5º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>Bre (Carlos Luiz Silva Brener)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Bre (Carlos Luiz Silva Brener) a cessão do(s) tempo(s) 1º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G176" s="6" t="inlineStr">
@@ -7606,32 +7610,32 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 4º de Hist para a prova de Qui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7643,27 +7647,27 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Sex, semana 14)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G178" s="6" t="inlineStr">
@@ -7675,12 +7679,12 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -7705,44 +7709,40 @@
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
-        <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
+          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr"/>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C2 (professor comum, tempos coordenados)</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7754,32 +7754,32 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11º tempo(s) (Ter, semana 4)</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -7791,23 +7791,23 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>9º, 10º tempo(s) (Ter, semana 4)</t>
+          <t>2º tempo(s) (Qui, semana 4)</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr"/>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 9º, 10º de Aprof. para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
@@ -7824,27 +7824,27 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>11º tempo(s) (Ter, semana 4)</t>
+          <t>4º tempo(s) (Seg, semana 5)</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 11º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -7861,23 +7861,27 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 4)</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr"/>
+          <t>5º tempo(s) (Seg, semana 5)</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>Isb (Isabela Gomes Bustamante)</t>
+        </is>
+      </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -7894,32 +7898,28 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr"/>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 4º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -7931,27 +7931,23 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 5)</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
-        </is>
-      </c>
+          <t>12º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr"/>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Proj.Vestibular</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
@@ -7968,28 +7964,32 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Ter, semana 5)</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8001,23 +8001,27 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>12º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr"/>
+          <t>2º tempo(s) (Sex, semana 6)</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>Deb (Debora Borba Linhares)</t>
+        </is>
+      </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Proj.Vestibular</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 12º de Proj.Vestibular para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
@@ -8034,27 +8038,27 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3º tempo(s) (Sex, semana 6)</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -8071,32 +8075,32 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Sex, semana 6)</t>
+          <t>5º tempo(s) (Seg, semana 7)</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8108,27 +8112,27 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 6)</t>
+          <t>2º tempo(s) (Ter, semana 7)</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -8145,27 +8149,27 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 7)</t>
+          <t>10º tempo(s) (Qui, semana 9)</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>DaF</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º de Ing para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
@@ -8182,27 +8186,27 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 7)</t>
+          <t>1º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -8219,32 +8223,32 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qui, semana 9)</t>
+          <t>3º tempo(s) (Sex, semana 10)</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Geo</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen) a cessão do(s) tempo(s) 10º de DaF para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8256,27 +8260,23 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Hist / Wag (Wagner Pinto da Silva)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Sex, semana 10)</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr">
-        <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
-        </is>
-      </c>
+          <t>10º tempo(s) (Ter, semana 12)</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr"/>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 1º de Hist para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -8293,27 +8293,27 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / AMu (André Barros Mucci), Deb (Debora Borba Linhares)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Sex, semana 10)</t>
+          <t>10º tempo(s) (Qua, semana 12)</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 3º de Geo para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
         </is>
       </c>
       <c r="G196" s="6" t="inlineStr">
@@ -8330,23 +8330,27 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Hist / Wag (Wagner Pinto da Silva)</t>
+          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 12)</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>Wag (Wagner Pinto da Silva)</t>
+        </is>
+      </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º de Aprof. para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -8363,27 +8367,23 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Qua, semana 12)</t>
-        </is>
-      </c>
-      <c r="D198" s="6" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
+          <t>2º tempo(s) (Qui, semana 13)</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr"/>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Artes</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 10º de Port para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
         </is>
       </c>
       <c r="G198" s="6" t="inlineStr">
@@ -8400,32 +8400,32 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Soc / Kle (André Luiz Medeiros Klevenhusen)</t>
+          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 13)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Wag (Wagner Pinto da Silva)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Wag (Wagner Pinto da Silva) a cessão do(s) tempo(s) 2º de Hist para a prova de Soc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 12C1</t>
         </is>
       </c>
     </row>
@@ -8437,23 +8437,27 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qui, semana 13)</t>
-        </is>
-      </c>
-      <c r="D200" s="6" t="inlineStr"/>
+          <t>1º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>Cadu (Carlos Eduardo Lima)</t>
+        </is>
+      </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Artes</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 2º de Artes para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
         </is>
       </c>
       <c r="G200" s="6" t="inlineStr">
@@ -8470,32 +8474,32 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Eth (Ethel Vera Figur Driesen)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 12C1</t>
+          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8507,27 +8511,27 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Ter, semana 14)</t>
+          <t>4º tempo(s) (Sex, semana 14)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
         </is>
       </c>
       <c r="G202" s="6" t="inlineStr">
@@ -8544,32 +8548,32 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 14)</t>
+          <t>5º, 6º tempo(s) (Seg, semana 15)</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Deb (Debora Borba Linhares)</t>
+          <t>Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Ing</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º, 6º de Ing para a prova de Geo</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
+          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -8581,27 +8585,27 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva), Fab (Fabio Merçon)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>4º tempo(s) (Sex, semana 14)</t>
+          <t>1º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>AMu (André Barros Mucci)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 4º de Redação para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
         </is>
       </c>
       <c r="G204" s="6" t="inlineStr">
@@ -8618,111 +8622,37 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>5º, 6º tempo(s) (Seg, semana 15)</t>
+          <t>2º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Isb (Isabela Gomes Bustamante)</t>
+          <t>Deb (Debora Borba Linhares)</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Ing</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Isb (Isabela Gomes Bustamante) a cessão do(s) tempo(s) 5º, 6º de Ing para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>⚠ Cruza o intervalo do recreio — nenhuma outra combinação coube; Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="5" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B206" s="6" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C206" s="5" t="inlineStr">
-        <is>
-          <t>1º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D206" s="6" t="inlineStr">
-        <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
-        </is>
-      </c>
-      <c r="E206" s="5" t="inlineStr">
-        <is>
-          <t>Fis</t>
-        </is>
-      </c>
-      <c r="F206" s="6" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 1º de Fis para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G206" s="6" t="inlineStr">
-        <is>
           <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>12C2</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener), JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>2º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>Deb (Debora Borba Linhares)</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>Solicitar ao(à) prof(a). Deb (Debora Borba Linhares) a cessão do(s) tempo(s) 2º de Port para a prova de Mat</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 12C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G207"/>
+  <autoFilter ref="A2:G205"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -8736,7 +8666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8782,17 +8712,17 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
@@ -8804,17 +8734,17 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 3)</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
@@ -8831,12 +8761,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
+          <t>cedeu aula na semana 10 tendo prova própria na semana 10</t>
         </is>
       </c>
     </row>
@@ -8853,12 +8783,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
@@ -8875,12 +8805,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 12</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
@@ -8897,12 +8827,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Geo / Mlo (Marcelo Rios Lopes)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 10 tendo prova própria na semana 10</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8849,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
         </is>
       </c>
     </row>
@@ -8941,12 +8871,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
         </is>
       </c>
     </row>
@@ -8963,12 +8893,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>Redação / BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
+          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -8980,83 +8910,83 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Redação / BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 12 tendo prova própria na semana 13</t>
+          <t>cedeu 6 de 54 aulas (11.1%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Fis / VSi (Vinícius de Paula Silveira)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>cedeu 3 de 26 aulas (11.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>GL / EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Car (Carina Campagnani), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 28 aulas (14.3%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>10C1</t>
+          <t>10C2</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Ing / APa (Ana Patricia Machado de Pinho Garcia)</t>
+          <t>Port / MFo (Mário Henrique Fonseca)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>cedeu 6 de 54 aulas (11.1%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 13 tendo prova própria na semana 13</t>
         </is>
       </c>
     </row>
@@ -9073,78 +9003,78 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Redação / BPad (Beatriz de Matos Ferreira Padrão)</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 14</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>DaF / Eth (Ethel Vera Figur Driesen), EFr (Wera Elisabeth Catharina Fricke Bispo Oliveira), Swa (Greta Schwankhaus Oliveira)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 5 tendo prova própria na semana 6</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Port / MFo (Mário Henrique Fonseca)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 13 tendo prova própria na semana 13</t>
+          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 3)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>10C2</t>
+          <t>11C1</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Redação / BPad (Beatriz de Matos Ferreira Padrão)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 5</t>
+          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
@@ -9156,17 +9086,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
         </is>
       </c>
     </row>
@@ -9178,24 +9108,24 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 3)</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -9205,19 +9135,19 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t xml:space="preserve">Ed.Física / </t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -9239,7 +9169,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>11C1</t>
+          <t>11C2</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -9261,7 +9191,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -9271,19 +9201,19 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Redação / AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -9293,41 +9223,41 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>Mat / Bre (Carlos Luiz Silva Brener)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 7 tendo prova própria na semana 8</t>
+          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>11C2</t>
+          <t>12C1</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ed.Física / </t>
+          <t>Redação / AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>12C2</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -9337,41 +9267,41 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Redação / AMu (André Barros Mucci)</t>
+          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 3 (meta: no máximo 2)</t>
+          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
+          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Mat / Bre (Carlos Luiz Silva Brener)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 14 tendo prova própria na semana 15</t>
+          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>12C1</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -9381,41 +9311,41 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Redação / AMu (André Barros Mucci)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 4 tendo prova própria na semana 4</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>12C2</t>
+          <t>9C1</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Ing / Isb (Isabela Gomes Bustamante)</t>
+          <t>Port / Jana (Janaína Souza Silva)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>tem 3 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
+          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -9437,7 +9367,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -9447,34 +9377,34 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 6</t>
+          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>9C1</t>
+          <t>9C2</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
+          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
+          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
+          <t>cedeu aula na semana 15 tendo prova própria na semana 16</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9416,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Regra 1 (teto de cessões por disciplina no semestre)</t>
+          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -9496,78 +9426,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>tem 2 aulas semanais e cedeu 4 (meta: no máximo 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>cedeu aula na semana 6 tendo prova própria na semana 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Regra 4 (não ceder às vésperas da própria prova)</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Mat / BrSa (Bruno Vianna dos Santos)</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>cedeu aula na semana 15 tendo prova própria na semana 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>9C2</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Regra 5 (teto de 11% das aulas programadas no semestre)</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Port / Jana (Janaína Souza Silva)</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
           <t>cedeu 4 de 32 aulas (12.5%) — acima do teto de 11%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D38"/>
+  <autoFilter ref="A2:D35"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
+++ b/Horario desenvolvido/Relatorio_trocas_de_tempo.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Provas coordenadas'!$A$2:$C$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$205</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trocas de tempo'!$A$2:$G$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regras relaxadas'!$A$2:$D$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G205"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4928,22 +4928,22 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 5)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -5462,32 +5462,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 12)</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 13)</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr"/>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C2</t>
         </is>
       </c>
     </row>
@@ -5499,28 +5495,32 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 13)</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C2</t>
+          <t>Prova conjunta com 11C2 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -5932,22 +5932,22 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 5)</t>
+          <t>2º tempo(s) (Ter, semana 5)</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -5964,23 +5964,27 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Ter, semana 5)</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
+        </is>
+      </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 3º de Qui para a prova de Hist</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -5997,27 +6001,23 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Ter, semana 6)</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>JJ (João Jorge Fernandes Chaves)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 5)</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr"/>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
@@ -6034,28 +6034,32 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Qui / CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>7º tempo(s) (Qua, semana 6)</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 6)</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Qui</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6067,32 +6071,28 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>DaF / CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>3º tempo(s) (Seg, semana 7)</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
-        </is>
-      </c>
+          <t>7º tempo(s) (Qua, semana 6)</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr"/>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 7º de Aprof. para a prova de DaF</t>
         </is>
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6104,28 +6104,32 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 7)</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr"/>
+          <t>3º tempo(s) (Seg, semana 7)</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>ClaMe (Clarissa Duarte Loureiro de Melo)</t>
+        </is>
+      </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). ClaMe (Clarissa Duarte Loureiro de Melo) a cessão do(s) tempo(s) 3º de Mat para a prova de Bio</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6137,32 +6141,28 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
+          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qui, semana 7)</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>AMu (André Barros Mucci)</t>
-        </is>
-      </c>
+          <t>5º tempo(s) (Qua, semana 7)</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr"/>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Aprof.</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+          <t>Grupo paralelo já combinado com 11C1</t>
         </is>
       </c>
     </row>
@@ -6174,27 +6174,27 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
+          <t>Fis / Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Seg, semana 8)</t>
+          <t>5º tempo(s) (Qui, semana 7)</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Ale (Alexandre de Almeida Pereira)</t>
+          <t>AMu (André Barros Mucci)</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
+          <t>Solicitar ao(à) prof(a). AMu (André Barros Mucci) a cessão do(s) tempo(s) 5º de Port para a prova de Fis</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -6211,27 +6211,27 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
+          <t>Mat / ClaMe (Clarissa Duarte Loureiro de Melo), JJ (João Jorge Fernandes Chaves)</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Qua, semana 8)</t>
+          <t>2º tempo(s) (Seg, semana 8)</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>Cadu (Carlos Eduardo Lima)</t>
+          <t>Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Fis</t>
+          <t>Bio</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
+          <t>Solicitar ao(à) prof(a). Ale (Alexandre de Almeida Pereira) a cessão do(s) tempo(s) 2º de Bio para a prova de Mat</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -6248,27 +6248,27 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Fil / LAn (Luiz Antônio Andrade de Oliveira)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>2º tempo(s) (Qua, semana 10)</t>
+          <t>9º tempo(s) (Qua, semana 8)</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Ver (Verena Alberti)</t>
+          <t>Cadu (Carlos Eduardo Lima)</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Fis</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Cadu (Carlos Eduardo Lima) a cessão do(s) tempo(s) 9º de Fis para a prova de Fil</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -6285,30 +6285,34 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
+          <t>Geo / Mar (Marcelo Alonso Morais)</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Seg, semana 12)</t>
+          <t>2º tempo(s) (Qua, semana 10)</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr"/>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 2º de Hist para a prova de Geo</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -6318,34 +6322,30 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Hist / Ver (Verena Alberti)</t>
+          <t>Ing / PaH (Paulo Henrique Sá Júnior)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>1º tempo(s) (Qua, semana 12)</t>
+          <t>5º tempo(s) (Seg, semana 12)</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Mar (Marcelo Alonso Morais)</t>
+          <t>CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Geo</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Mar (Marcelo Alonso Morais) a cessão do(s) tempo(s) 1º de Geo para a prova de Hist</t>
-        </is>
-      </c>
-      <c r="G141" s="4" t="inlineStr">
-        <is>
-          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
-        </is>
-      </c>
+          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab) a cessão do(s) tempo(s) 5º de GL para a prova de Ing</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -6388,23 +6388,27 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr"/>
+          <t>2º tempo(s) (Ter, semana 14)</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>JJ (João Jorge Fernandes Chaves)</t>
+        </is>
+      </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Ed.Física</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
+          <t>Solicitar ao(à) prof(a). JJ (João Jorge Fernandes Chaves) a cessão do(s) tempo(s) 2º de Mat para a prova de Hist</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -6421,27 +6425,27 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>Hist / Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>9º tempo(s) (Ter, semana 15)</t>
+          <t>3º tempo(s) (Ter, semana 14)</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+          <t>CAl (Carlos Alberto Linhares da Silva)</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Redação</t>
+          <t>Qui</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a). CAl (Carlos Alberto Linhares da Silva) a cessão do(s) tempo(s) 3º de Qui para a prova de Hist</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
@@ -6458,27 +6462,23 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
+          <t>LP/LIT/RED / ACo (Alexandre Braga Badaue Coelho), AMu (André Barros Mucci), Raf (Rafael Alverne Freitas de Albuquerque)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>10º tempo(s) (Ter, semana 15)</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>Ver (Verena Alberti)</t>
-        </is>
-      </c>
+          <t>10º, 11º tempo(s) (Qui, semana 14)</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr"/>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Hist</t>
+          <t>Ed.Física</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
+          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 10º, 11º de Ed.Física para a prova de LP/LIT/RED</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -6495,28 +6495,32 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>GL / CBu (Claudia Burkhardt), Swa (Greta Schwankhaus Oliveira), SGa (Sabrina Gab)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>5º tempo(s) (Qua, semana 15)</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr"/>
+          <t>9º tempo(s) (Ter, semana 15)</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>ACo (Alexandre Braga Badaue Coelho)</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Aprof.</t>
+          <t>Redação</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a).  a cessão do(s) tempo(s) 5º de Aprof. para a prova de GL</t>
+          <t>Solicitar ao(à) prof(a). ACo (Alexandre Braga Badaue Coelho) a cessão do(s) tempo(s) 9º de Redação para a prova de Bio</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
         <is>
-          <t>Grupo paralelo já combinado com 11C1</t>
+          <t>Prova conjunta com 11C1 (professor comum, tempos coordenados)</t>
         </is>
       </c>
     </row>
@@ -6528,27 +6532,27 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Geo / Mar (Marcelo Alonso Morais)</t>
+          <t>Bio / Ale (Alexandre de Almeida Pereira)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>6º tempo(s) (Seg, semana 16)</t>
+          <t>10º tempo(s) (Ter, semana 15)</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira)</t>
+          <t>Ver (Verena Alberti)</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>DaF</t>
+          <t>Hist</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Solicitar ao(à) prof(a). CBu (Claudia Burkhardt), SGa (Sabrina Gab), Swa (Greta Schwankhaus Oliveira) a cessão do(s) tempo(s) 6º de DaF para a prova de Geo</t>
+          <t>Solicitar ao(à) prof(a). Ver (Verena Alberti) a cessão do(s) tempo(s) 10º de Hist para a prova de Bio</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -6565,32 +6569,28 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Mat / ClaMe (Clarissa Duarte 